--- a/src/src/main/webapp/portal/zkb/salesPerson/excel/APM_ZKB_SalePerson_Exp_Template.xlsx
+++ b/src/src/main/webapp/portal/zkb/salesPerson/excel/APM_ZKB_SalePerson_Exp_Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Intellij Idea\codes\hc-apm-web\src\src\main\webapp\portal\zkb\salesPerson\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B154382-E049-4DE0-B6B1-0D8EF97457D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E277DD2-069A-44F0-A7CB-3F1A76525D9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="358" xr2:uid="{DFA98752-8825-45D1-95EF-55416474EBE9}"/>
   </bookViews>
@@ -391,18 +391,18 @@
   <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="24" customWidth="1"/>
-    <col min="2" max="2" width="31.28515625" customWidth="1"/>
+    <col min="1" max="1" width="31.28515625" customWidth="1"/>
+    <col min="2" max="2" width="36.140625" customWidth="1"/>
     <col min="12" max="12" width="20.28515625" customWidth="1"/>
     <col min="13" max="13" width="21.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
